--- a/contact_forms/030_student_emergency_contact_form--contact_forms.xlsx
+++ b/contact_forms/030_student_emergency_contact_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -626,7 +626,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Format: XXX-XXXX</t>
+          <t>Format - XXX-XXXX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Format: name@domain.com</t>
+          <t>Format - name@domain.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Format: XXXX</t>
+          <t>Format - XXXX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Emergency Phone Number</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Format: XXX-XXXX</t>
+          <t>Format - XXX-XXXX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Relationship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Emergency Address</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Emergency City</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Emergency State</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -936,12 +936,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Emergency Zip</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Format: XXXX</t>
+          <t>Format - XXXX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Emergency Relationship Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>emergency_phone_number</t>
+          <t>emergency_phone_number_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Emergency Phone Number 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Format: XXX-XXXX</t>
+          <t>Format - XXX-XXXX</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Emergency Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Format: name@domain.com</t>
+          <t>Format - name@domain.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
